--- a/outputs/EVINV-POC-001/phase4/phase4-dfm-standards-audit.xlsx
+++ b/outputs/EVINV-POC-001/phase4/phase4-dfm-standards-audit.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 4 | Gate: 4 | Generated: 2026-08-18T13:03:02.205Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 4 | Gate: 4 | Generated: 2026-08-18T19:54:08.531Z</v>
       </c>
     </row>
     <row r="4">
